--- a/diseases/d145/2020-2025.xlsx
+++ b/diseases/d145/2020-2025.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1669,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2414,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3159,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3904,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4772,6 +4797,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5512,6 +5542,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6400,6 +6435,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7140,6 +7180,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7880,6 +7925,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8768,6 +8818,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9508,6 +9563,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10248,6 +10308,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11136,6 +11201,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11876,6 +11946,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12616,6 +12691,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13504,6 +13584,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14244,6 +14329,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14984,6 +15074,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15872,6 +15967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16612,6 +16712,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17352,6 +17457,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18240,6 +18350,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18980,6 +19095,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19868,6 +19988,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20608,6 +20733,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21348,6 +21478,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22088,6 +22223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22976,6 +23116,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23716,6 +23861,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24456,6 +24606,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25344,6 +25499,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26084,6 +26244,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26972,6 +27137,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27712,6 +27882,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28452,6 +28627,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29340,6 +29520,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30080,6 +30265,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30820,6 +31010,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31708,6 +31903,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32448,6 +32648,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33188,6 +33393,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34076,6 +34286,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34816,6 +35031,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35556,6 +35776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36444,6 +36669,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37184,6 +37414,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37924,6 +38159,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38812,6 +39052,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39552,6 +39797,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40292,6 +40542,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41180,6 +41435,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41920,6 +42180,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42808,6 +43073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43548,6 +43818,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO291" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44288,6 +44563,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO296" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45176,6 +45456,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO302" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45916,6 +46201,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO307" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46656,6 +46946,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47544,6 +47839,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48284,6 +48584,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO323" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49172,6 +49477,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO329" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49912,6 +50222,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO334" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50652,6 +50967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO339" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51392,6 +51712,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO344" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52280,6 +52605,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO350" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53020,6 +53350,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO355" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53760,6 +54095,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO360" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54648,6 +54988,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA366" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO366" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55388,6 +55733,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO371" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56276,6 +56626,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO377" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57014,6 +57369,11 @@
       <c r="S382" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO382" t="inlineStr">
